--- a/reports/Table3_Treatment_Effect.xlsx
+++ b/reports/Table3_Treatment_Effect.xlsx
@@ -447,7 +447,7 @@
     <col width="33" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
@@ -585,15 +585,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.195</v>
+        <v>3.526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.101–14.153</t>
+          <t>0.604–20.595</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8878</v>
+        <v>0.1617</v>
       </c>
       <c r="F4" t="n">
         <v/>
@@ -602,7 +602,7 @@
         <v/>
       </c>
       <c r="H4" t="n">
-        <v>1.195</v>
+        <v>3.526</v>
       </c>
       <c r="I4" t="n">
         <v>69</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1058</v>
+        <v>-0.1291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3384</v>
+        <v>0.2863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1058</v>
+        <v>-0.1291</v>
       </c>
       <c r="G5" t="n">
         <v/>
       </c>
       <c r="H5" t="n">
-        <v>0.576</v>
+        <v>2.814</v>
       </c>
       <c r="I5" t="n">
         <v>69</v>
@@ -659,14 +659,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.186–1.781</t>
+          <t>0.42–18.844</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7896</v>
+        <v>0.7796</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6837</v>
+        <v>0.9087</v>
       </c>
     </row>
     <row r="6">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1407</v>
+        <v>-0.1585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.209</v>
+        <v>0.2391</v>
       </c>
       <c r="F6" t="n">
         <v/>
       </c>
       <c r="G6" t="n">
-        <v>0.1407</v>
+        <v>-0.1585</v>
       </c>
       <c r="H6" t="n">
-        <v>0.517</v>
+        <v>3.431</v>
       </c>
       <c r="I6" t="n">
         <v>69</v>
@@ -708,7 +708,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.184–1.447</t>
+          <t>0.441–26.714</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1955</v>
+        <v>-0.1867</v>
       </c>
       <c r="D7" t="n">
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>0.2399</v>
+        <v>0.0436</v>
       </c>
       <c r="F7" t="n">
         <v/>
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="H7" t="n">
-        <v>0.236</v>
+        <v>7.865</v>
       </c>
       <c r="I7" t="n">
         <v>69</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.021–2.626</t>
+          <t>1.061–58.299</t>
         </is>
       </c>
       <c r="L7" t="n">
